--- a/docs/design-docs/02_画面設計書_マスタ管理.xlsx
+++ b/docs/design-docs/02_画面設計書_マスタ管理.xlsx
@@ -13,7 +13,678 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="223">
+  <si>
+    <t>版数</t>
+  </si>
+  <si>
+    <t>改訂日</t>
+  </si>
+  <si>
+    <t>改訂内容</t>
+  </si>
+  <si>
+    <t>改訂者</t>
+  </si>
+  <si>
+    <t>承認者</t>
+  </si>
+  <si>
+    <t>区分</t>
+  </si>
+  <si>
+    <t>備考</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>2026/05/23</t>
+  </si>
+  <si>
+    <t>初版作成</t>
+  </si>
+  <si>
+    <t>システム開発部</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>新規</t>
+  </si>
+  <si>
+    <t>画面設計書 — 設備マスタ一覧</t>
+  </si>
+  <si>
+    <t>文書管理情報</t>
+  </si>
+  <si>
+    <t>システムID</t>
+  </si>
+  <si>
+    <t>STRUTSLAB-001</t>
+  </si>
+  <si>
+    <t>サブシステム名</t>
+  </si>
+  <si>
+    <t>マスタ管理</t>
+  </si>
+  <si>
+    <t>画面ID</t>
+  </si>
+  <si>
+    <t>SCR-MST-EQP-001</t>
+  </si>
+  <si>
+    <t>画面名</t>
+  </si>
+  <si>
+    <t>設備マスタ一覧</t>
+  </si>
+  <si>
+    <t>プログラムID</t>
+  </si>
+  <si>
+    <t>PG-MST-EQP-001</t>
+  </si>
+  <si>
+    <t>文書番号</t>
+  </si>
+  <si>
+    <t>DOC-SCR-SCR-MST-EQP-001</t>
+  </si>
+  <si>
+    <t>作成日</t>
+  </si>
+  <si>
+    <t>作成者</t>
+  </si>
+  <si>
+    <t>画面レイアウト</t>
+  </si>
+  <si>
+    <t>上部：検索条件（設備種別select, 電圧階級select, 設置年from/to, 保全ランクselect, 担当部署text）。検索/クリアボタン。
+下部：一覧テーブル（設備コード, 設備名, 設備種別, 電圧階級, 設置年月, 保全ランク, 担当部署）。ページング。CSV出力, 選択削除, 新規登録ボタン。各行にcheckbox。</t>
+  </si>
+  <si>
+    <t>画面要素一覧</t>
+  </si>
+  <si>
+    <t>要素ID</t>
+  </si>
+  <si>
+    <t>種別</t>
+  </si>
+  <si>
+    <t>表示名</t>
+  </si>
+  <si>
+    <t>入力値/選択肢</t>
+  </si>
+  <si>
+    <t>説明</t>
+  </si>
+  <si>
+    <t>テスト難点タグ</t>
+  </si>
+  <si>
+    <t>eqp-search-type</t>
+  </si>
+  <si>
+    <t>select</t>
+  </si>
+  <si>
+    <t>設備種別</t>
+  </si>
+  <si>
+    <t>変圧器/遮断器/開閉器/ケーブル/母線/保護継電器/計器用変成器</t>
+  </si>
+  <si>
+    <t>5条件AND検索</t>
+  </si>
+  <si>
+    <t>複合検索</t>
+  </si>
+  <si>
+    <t>eqp-search-voltage</t>
+  </si>
+  <si>
+    <t>電圧階級</t>
+  </si>
+  <si>
+    <t>66kV/154kV/275kV/500kV</t>
+  </si>
+  <si>
+    <t>eqp-search-year-from</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>設置年(from)</t>
+  </si>
+  <si>
+    <t>YYYY</t>
+  </si>
+  <si>
+    <t>from&amp;gt;toバリデーション</t>
+  </si>
+  <si>
+    <t>eqp-search-year-to</t>
+  </si>
+  <si>
+    <t>設置年(to)</t>
+  </si>
+  <si>
+    <t>eqp-search-rank</t>
+  </si>
+  <si>
+    <t>保全ランク</t>
+  </si>
+  <si>
+    <t>S/A/B/C</t>
+  </si>
+  <si>
+    <t>eqp-search-dept</t>
+  </si>
+  <si>
+    <t>担当部署</t>
+  </si>
+  <si>
+    <t>部分一致</t>
+  </si>
+  <si>
+    <t>eqp-select-all</t>
+  </si>
+  <si>
+    <t>checkbox</t>
+  </si>
+  <si>
+    <t>全選択</t>
+  </si>
+  <si>
+    <t>当該ページのみ全選択</t>
+  </si>
+  <si>
+    <t>全選択scope検証</t>
+  </si>
+  <si>
+    <t>eqp-check-{n}</t>
+  </si>
+  <si>
+    <t>選択</t>
+  </si>
+  <si>
+    <t>指数付きname属性</t>
+  </si>
+  <si>
+    <t>eqp-code-{n}</t>
+  </si>
+  <si>
+    <t>link</t>
+  </si>
+  <si>
+    <t>設備コード</t>
+  </si>
+  <si>
+    <t>クリック→編集画面</t>
+  </si>
+  <si>
+    <t>eqp-btn-csv</t>
+  </si>
+  <si>
+    <t>submit</t>
+  </si>
+  <si>
+    <t>CSV出力</t>
+  </si>
+  <si>
+    <t>Content-Disposition検証</t>
+  </si>
+  <si>
+    <t>eqp-btn-delete</t>
+  </si>
+  <si>
+    <t>選択削除</t>
+  </si>
+  <si>
+    <t>window.confirm</t>
+  </si>
+  <si>
+    <t>confirm OK/Cancel</t>
+  </si>
+  <si>
+    <t>eqp-btn-new</t>
+  </si>
+  <si>
+    <t>新規登録</t>
+  </si>
+  <si>
+    <t>eqp-paging</t>
+  </si>
+  <si>
+    <t>ページング</t>
+  </si>
+  <si>
+    <t>前へ 1 2 3 … 次へ</t>
+  </si>
+  <si>
+    <t>ページ跨ぎ不可</t>
+  </si>
+  <si>
+    <t>テーブル列定義</t>
+  </si>
+  <si>
+    <t>列名</t>
+  </si>
+  <si>
+    <t>型</t>
+  </si>
+  <si>
+    <t>ソート</t>
+  </si>
+  <si>
+    <t>VARCHAR</t>
+  </si>
+  <si>
+    <t>○</t>
+  </si>
+  <si>
+    <t>設備名</t>
+  </si>
+  <si>
+    <t>設置年月</t>
+  </si>
+  <si>
+    <t>CHAR</t>
+  </si>
+  <si>
+    <t>Struts1マッピング</t>
+  </si>
+  <si>
+    <t>項目</t>
+  </si>
+  <si>
+    <t>値</t>
+  </si>
+  <si>
+    <t>Action Path</t>
+  </si>
+  <si>
+    <t>/mst/eqp/list</t>
+  </si>
+  <si>
+    <t>Action Class</t>
+  </si>
+  <si>
+    <t>EqpListAction</t>
+  </si>
+  <si>
+    <t>Form Bean</t>
+  </si>
+  <si>
+    <t>EqpSearchForm</t>
+  </si>
+  <si>
+    <t>Forward</t>
+  </si>
+  <si>
+    <t>eqp.list.tiles</t>
+  </si>
+  <si>
+    <t>テスト難点詳細</t>
+  </si>
+  <si>
+    <t>多段検索(5条件AND)：全組合せ検索結果検証</t>
+  </si>
+  <si>
+    <t>全選択checkbox：page内のみ選択、他page無影響</t>
+  </si>
+  <si>
+    <t>CSV出力：検索条件に応じた出力内容確認</t>
+  </si>
+  <si>
+    <t>選択削除：confirm dialog OK/Cancel両方</t>
+  </si>
+  <si>
+    <t>画面設計書 — 設備マスタ登録・編集</t>
+  </si>
+  <si>
+    <t>SCR-MST-EQP-002</t>
+  </si>
+  <si>
+    <t>設備マスタ登録・編集</t>
+  </si>
+  <si>
+    <t>PG-MST-EQP-002</t>
+  </si>
+  <si>
+    <t>DOC-SCR-SCR-MST-EQP-002</t>
+  </si>
+  <si>
+    <t>5セクション大フォーム（基本情報/電気仕様/設置場所/保全区分/備考）。セクション間アンカーリンク。親設備選択Popup→値反映。添付ファイル。</t>
+  </si>
+  <si>
+    <t>eqp-name</t>
+  </si>
+  <si>
+    <t>必須</t>
+  </si>
+  <si>
+    <t>eqp-type</t>
+  </si>
+  <si>
+    <t>変圧器/遮断器/…</t>
+  </si>
+  <si>
+    <t>eqp-status</t>
+  </si>
+  <si>
+    <t>設備ステータス</t>
+  </si>
+  <si>
+    <t>運用中/停止中/廃止</t>
+  </si>
+  <si>
+    <t>廃止→親設備不可</t>
+  </si>
+  <si>
+    <t>eqp-voltage</t>
+  </si>
+  <si>
+    <t>eqp-parent</t>
+  </si>
+  <si>
+    <t>親設備</t>
+  </si>
+  <si>
+    <t>読取専用</t>
+  </si>
+  <si>
+    <t>Popup選択結果</t>
+  </si>
+  <si>
+    <t>Stale Element</t>
+  </si>
+  <si>
+    <t>eqp-parent-btn</t>
+  </si>
+  <si>
+    <t>button</t>
+  </si>
+  <si>
+    <t>window.open→選択→opener反映</t>
+  </si>
+  <si>
+    <t>Window handle切替</t>
+  </si>
+  <si>
+    <t>eqp-interval</t>
+  </si>
+  <si>
+    <t>点検周期(月)</t>
+  </si>
+  <si>
+    <t>1〜120</t>
+  </si>
+  <si>
+    <t>eqp-file</t>
+  </si>
+  <si>
+    <t>file</t>
+  </si>
+  <si>
+    <t>添付</t>
+  </si>
+  <si>
+    <t>file size/形式制限</t>
+  </si>
+  <si>
+    <t>eqp-btn-save</t>
+  </si>
+  <si>
+    <t>登録/更新</t>
+  </si>
+  <si>
+    <t>POST→validation→遷移</t>
+  </si>
+  <si>
+    <t>eqp-btn-back</t>
+  </si>
+  <si>
+    <t>戻る</t>
+  </si>
+  <si>
+    <t>一覧へ</t>
+  </si>
+  <si>
+    <t>/mst/eqp/save</t>
+  </si>
+  <si>
+    <t>EqpSaveAction(DispatchAction)</t>
+  </si>
+  <si>
+    <t>EqpForm(ValidatorForm)</t>
+  </si>
+  <si>
+    <t>親設備選択Popup：Window handle→検索→選択→opener値反映</t>
+  </si>
+  <si>
+    <t>5セクションform：アンカー移動で値維持</t>
+  </si>
+  <si>
+    <t>廃止設備→親不可</t>
+  </si>
+  <si>
+    <t>添付+同時validation：error時file維持</t>
+  </si>
+  <si>
+    <t>画面設計書 — 点検項目マスタ一覧</t>
+  </si>
+  <si>
+    <t>SCR-MST-CHK-001</t>
+  </si>
+  <si>
+    <t>点検項目マスタ一覧</t>
+  </si>
+  <si>
+    <t>PG-MST-CHK-001</t>
+  </si>
+  <si>
+    <t>DOC-SCR-SCR-MST-CHK-001</t>
+  </si>
+  <si>
+    <t>上部検索：設備種別×点検種別(日常/定期/精密)。一覧：テンプレート名, 設備種別, 点検種別, 項目数, 最終更新日。各行に編集/コピー/削除。並順変更▲/▼。</t>
+  </si>
+  <si>
+    <t>chk-search-type</t>
+  </si>
+  <si>
+    <t>chk-search-kind</t>
+  </si>
+  <si>
+    <t>点検種別</t>
+  </si>
+  <si>
+    <t>日常/定期/精密</t>
+  </si>
+  <si>
+    <t>chk-tmpl-name-{n}</t>
+  </si>
+  <si>
+    <t>テンプレート名</t>
+  </si>
+  <si>
+    <t>クリック→編集</t>
+  </si>
+  <si>
+    <t>chk-btn-copy-{n}</t>
+  </si>
+  <si>
+    <t>コピー</t>
+  </si>
+  <si>
+    <t>copy後名称重複check</t>
+  </si>
+  <si>
+    <t>chk-btn-order-up-{n}</t>
+  </si>
+  <si>
+    <t>▲</t>
+  </si>
+  <si>
+    <t>並順上へ→index変化</t>
+  </si>
+  <si>
+    <t>stale element</t>
+  </si>
+  <si>
+    <t>chk-btn-order-down-{n}</t>
+  </si>
+  <si>
+    <t>▼</t>
+  </si>
+  <si>
+    <t>並順下へ→index変化</t>
+  </si>
+  <si>
+    <t>項目数</t>
+  </si>
+  <si>
+    <t>INT</t>
+  </si>
+  <si>
+    <t>最終更新日</t>
+  </si>
+  <si>
+    <t>DATE</t>
+  </si>
+  <si>
+    <t>/mst/chkitem/list</t>
+  </si>
+  <si>
+    <t>CheckItemListAction</t>
+  </si>
+  <si>
+    <t>CheckItemSearchForm</t>
+  </si>
+  <si>
+    <t>chkitem.list.tiles</t>
+  </si>
+  <si>
+    <t>並順変更：▲/▼後要素index変動(stale)</t>
+  </si>
+  <si>
+    <t>copy→名称重複validation</t>
+  </si>
+  <si>
+    <t>画面設計書 — 点検項目マスタ登録・編集</t>
+  </si>
+  <si>
+    <t>SCR-MST-CHK-002</t>
+  </si>
+  <si>
+    <t>点検項目マスタ登録・編集</t>
+  </si>
+  <si>
+    <t>PG-MST-CHK-002</t>
+  </si>
+  <si>
+    <t>DOC-SCR-SCR-MST-CHK-002</t>
+  </si>
+  <si>
+    <t>上部基本情報(テンプレート名/設備種別/点検種別)。3階層ツリー編集：大分類→中分類→項目。各行に追加/削除ボタン(Submit→再描画)。一括項目追加→行数指定→戻って追加。</t>
+  </si>
+  <si>
+    <t>chk-tmpl-name</t>
+  </si>
+  <si>
+    <t>chk-cat1-name-{n}</t>
+  </si>
+  <si>
+    <t>大分類名</t>
+  </si>
+  <si>
+    <t>chk-btn-add-cat1</t>
+  </si>
+  <si>
+    <t>+大分類追加</t>
+  </si>
+  <si>
+    <t>動的行追加(Submit)</t>
+  </si>
+  <si>
+    <t>index再振</t>
+  </si>
+  <si>
+    <t>chk-cat2-name-{n}-{m}</t>
+  </si>
+  <si>
+    <t>中分類名</t>
+  </si>
+  <si>
+    <t>Nested index</t>
+  </si>
+  <si>
+    <t>chk-btn-add-cat2-{n}</t>
+  </si>
+  <si>
+    <t>+中分類追加</t>
+  </si>
+  <si>
+    <t>chk-item-name-{i}</t>
+  </si>
+  <si>
+    <t>項目名</t>
+  </si>
+  <si>
+    <t>chk-item-criteria-{i}</t>
+  </si>
+  <si>
+    <t>判定基準</t>
+  </si>
+  <si>
+    <t>○のみ/○×△</t>
+  </si>
+  <si>
+    <t>chk-btn-del-{i}</t>
+  </si>
+  <si>
+    <t>削除</t>
+  </si>
+  <si>
+    <t>行削除→index再振</t>
+  </si>
+  <si>
+    <t>chk-btn-bulk-add</t>
+  </si>
+  <si>
+    <t>一括項目追加</t>
+  </si>
+  <si>
+    <t>別画面遷移→戻る</t>
+  </si>
+  <si>
+    <t>/mst/chkitem/save</t>
+  </si>
+  <si>
+    <t>CheckItemSaveAction</t>
+  </si>
+  <si>
+    <t>CheckItemForm(ValidatorForm)</t>
+  </si>
+  <si>
+    <t>3階層tree動的行追加：大分類→中分類→項目の順でindex変動</t>
+  </si>
+  <si>
+    <t>行削除後index再振：削除→追加繰返で連番維持</t>
+  </si>
+  <si>
+    <t>一括項目追加：別画面→戻る→追加data保持</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
